--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R3" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R4" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R3" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B4" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R4" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091021</v>
       </c>
       <c r="B2" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126091102</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126091084</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091021</v>
       </c>
       <c r="B2" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R3" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B4" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R4" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091021</v>
       </c>
       <c r="B2" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B3" t="n">
-        <v>80077</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R3" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R4" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091021</v>
       </c>
       <c r="B2" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>80081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R3" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B4" t="n">
-        <v>80077</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R4" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B3" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R3" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R4" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R3" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R4" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091021</v>
       </c>
       <c r="B2" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>126091102</v>
       </c>
       <c r="B3" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>126091084</v>
       </c>
       <c r="B4" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36293-2024 artfynd.xlsx
+++ b/artfynd/A 36293-2024 artfynd.xlsx
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126091102</v>
+        <v>126091084</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556740</v>
+        <v>556737</v>
       </c>
       <c r="R3" t="n">
-        <v>7227186</v>
+        <v>7227192</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091084</v>
+        <v>126091102</v>
       </c>
       <c r="B4" t="n">
-        <v>80084</v>
+        <v>80083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556737</v>
+        <v>556740</v>
       </c>
       <c r="R4" t="n">
-        <v>7227192</v>
+        <v>7227186</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
